--- a/addons/nhan_su/static/src/files/template_nhan_vien.xlsx
+++ b/addons/nhan_su/static/src/files/template_nhan_vien.xlsx
@@ -427,14 +427,14 @@
   <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
@@ -443,7 +443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mã Định Danh (*)</t>
+          <t>Mã Định Danh (Để trống tự tạo)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Loại Hợp Đồng (Thử việc/Có thời hạn/Không thời hạn)</t>
+          <t>Loại Hợp Đồng</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -498,11 +498,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NV001</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>Nguyễn Văn</t>
@@ -553,11 +549,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NV002</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>Trần Thị</t>
